--- a/data/trans_dic/PCS12_SP_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,42; 25,89</t>
+          <t>18,47; 26,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 28,57</t>
+          <t>20,72; 28,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,49; 22,92</t>
+          <t>14,75; 22,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 27,19</t>
+          <t>13,21; 26,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,15; 32,39</t>
+          <t>24,76; 32,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,05; 32,69</t>
+          <t>24,02; 32,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,09; 26,44</t>
+          <t>17,57; 25,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,75; 25,28</t>
+          <t>12,46; 25,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,5; 28,14</t>
+          <t>21,97; 28,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,48; 29,07</t>
+          <t>23,42; 29,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 22,79</t>
+          <t>16,95; 22,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,46; 24,05</t>
+          <t>14,47; 24,24</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,37; 26,95</t>
+          <t>20,69; 27,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,32; 31,49</t>
+          <t>24,39; 31,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 25,26</t>
+          <t>18,51; 25,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,92; 36,76</t>
+          <t>24,84; 36,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,53; 43,22</t>
+          <t>35,37; 43,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,13; 39,29</t>
+          <t>31,12; 38,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,82; 26,82</t>
+          <t>19,98; 27,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,18; 31,76</t>
+          <t>15,36; 31,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,45; 33,64</t>
+          <t>28,52; 33,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,81; 34,11</t>
+          <t>28,59; 34,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,54</t>
+          <t>20,2; 24,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,15; 32,21</t>
+          <t>21,68; 32,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,44; 37,85</t>
+          <t>30,32; 37,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,87; 39,44</t>
+          <t>32,24; 39,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,99; 27,8</t>
+          <t>20,71; 27,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,81; 38,6</t>
+          <t>30,13; 38,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,59; 52,17</t>
+          <t>44,61; 52,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,39; 48,17</t>
+          <t>40,87; 48,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,74; 37,93</t>
+          <t>30,36; 37,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,31; 40,51</t>
+          <t>33,66; 40,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,53; 44,39</t>
+          <t>39,05; 44,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,61; 43,34</t>
+          <t>37,57; 43,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,8; 31,45</t>
+          <t>26,36; 31,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 38,22</t>
+          <t>32,72; 38,24</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,71; 46,84</t>
+          <t>38,42; 47,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,42; 45,4</t>
+          <t>37,44; 45,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,11; 42,23</t>
+          <t>34,53; 42,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,31; 83,24</t>
+          <t>45,4; 83,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,8; 64,7</t>
+          <t>56,11; 64,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,94; 54,6</t>
+          <t>45,86; 54,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,77; 47,6</t>
+          <t>39,5; 48,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,7; 54,88</t>
+          <t>43,79; 54,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,06; 54,61</t>
+          <t>48,11; 54,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42,78; 48,8</t>
+          <t>42,72; 48,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38,35; 43,93</t>
+          <t>38,31; 44,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,74; 73,02</t>
+          <t>48,25; 74,11</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,36; 70,93</t>
+          <t>61,4; 71,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,08; 64,29</t>
+          <t>54,13; 64,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,44; 61,19</t>
+          <t>51,74; 61,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54,91; 62,55</t>
+          <t>55,28; 62,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>66,05; 74,93</t>
+          <t>65,53; 74,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,75; 74,69</t>
+          <t>66,11; 74,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,16; 67,29</t>
+          <t>58,3; 67,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,86; 67,14</t>
+          <t>60,71; 66,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,72; 71,44</t>
+          <t>65,11; 71,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,31; 68,11</t>
+          <t>61,36; 68,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56,1; 62,8</t>
+          <t>56,22; 63,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,92; 64,15</t>
+          <t>58,79; 63,66</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,82; 81,68</t>
+          <t>71,9; 81,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70,95; 81,15</t>
+          <t>71,02; 81,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,41; 73,44</t>
+          <t>63,09; 73,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58,95; 67,1</t>
+          <t>59,07; 67,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,97; 90,55</t>
+          <t>83,71; 90,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,67; 85,14</t>
+          <t>76,93; 85,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,24; 81,53</t>
+          <t>72,39; 81,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75,08; 93,39</t>
+          <t>75,51; 93,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79,72; 85,76</t>
+          <t>79,34; 85,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74,86; 81,69</t>
+          <t>74,96; 81,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69,45; 76,13</t>
+          <t>69,28; 76,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69,45; 87,15</t>
+          <t>69,32; 87,78</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,13; 94,17</t>
+          <t>86,23; 94,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,11; 91,71</t>
+          <t>82,0; 91,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,46; 85,82</t>
+          <t>77,23; 85,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76,61; 84,28</t>
+          <t>77,24; 83,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,11; 97,85</t>
+          <t>93,38; 97,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,44; 96,36</t>
+          <t>91,65; 96,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,52; 93,76</t>
+          <t>87,3; 93,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,73; 93,58</t>
+          <t>89,73; 93,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,43; 95,87</t>
+          <t>91,36; 95,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89,11; 93,7</t>
+          <t>89,14; 93,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84,61; 89,86</t>
+          <t>84,93; 90,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,36; 89,15</t>
+          <t>85,35; 89,06</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,98; 44,5</t>
+          <t>40,73; 44,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,18; 45,89</t>
+          <t>42,44; 45,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,42; 40,7</t>
+          <t>37,29; 40,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45,22; 61,45</t>
+          <t>45,41; 60,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,36; 58,85</t>
+          <t>55,21; 58,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,61; 56,21</t>
+          <t>52,67; 56,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,97; 49,62</t>
+          <t>46,23; 49,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,93; 63,17</t>
+          <t>50,94; 63,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,6; 51,16</t>
+          <t>48,72; 51,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48,01; 50,45</t>
+          <t>47,99; 50,47</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42,23; 44,64</t>
+          <t>42,19; 44,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,01; 58,43</t>
+          <t>49,02; 58,99</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91008; 127915</t>
+          <t>91246; 129428</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91419; 129735</t>
+          <t>94077; 131573</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60770; 96128</t>
+          <t>61876; 94909</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53991; 108755</t>
+          <t>52854; 107285</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>112880; 151403</t>
+          <t>115759; 151828</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>103451; 140644</t>
+          <t>103348; 140516</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71583; 104620</t>
+          <t>69523; 101529</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39716; 78789</t>
+          <t>38814; 78722</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>216313; 270587</t>
+          <t>211240; 270100</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>207641; 257051</t>
+          <t>207106; 260054</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140368; 185783</t>
+          <t>138144; 185355</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>102888; 171172</t>
+          <t>102970; 172524</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149794; 198180</t>
+          <t>152162; 200650</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>167111; 216336</t>
+          <t>167551; 218839</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109942; 149148</t>
+          <t>109295; 150724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105533; 155689</t>
+          <t>105211; 154688</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>222243; 270346</t>
+          <t>221239; 270853</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>189943; 239787</t>
+          <t>189886; 237531</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>111686; 151148</t>
+          <t>112602; 152634</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77541; 162305</t>
+          <t>78466; 161511</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>387240; 457872</t>
+          <t>388090; 456999</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>373800; 442490</t>
+          <t>370970; 443208</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>232960; 294712</t>
+          <t>233131; 288277</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>197668; 300993</t>
+          <t>202569; 300776</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>194395; 241717</t>
+          <t>193646; 240804</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>217299; 268944</t>
+          <t>219820; 269913</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140417; 185994</t>
+          <t>138575; 183952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159607; 206676</t>
+          <t>161319; 206187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>307577; 359807</t>
+          <t>307675; 360907</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>287134; 342443</t>
+          <t>290517; 343678</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>203313; 250847</t>
+          <t>200820; 250643</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>180475; 219479</t>
+          <t>182360; 217927</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>511825; 589669</t>
+          <t>518760; 589699</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>523805; 603625</t>
+          <t>523238; 602145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>356612; 418472</t>
+          <t>350704; 419798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>352947; 411689</t>
+          <t>352429; 411884</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>195770; 243158</t>
+          <t>199473; 248726</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>230001; 279067</t>
+          <t>230124; 280198</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>220343; 272810</t>
+          <t>223100; 273604</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>401311; 737282</t>
+          <t>402082; 740869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>287727; 333606</t>
+          <t>289338; 332661</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>283072; 336471</t>
+          <t>282596; 333501</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>258166; 308973</t>
+          <t>256359; 311761</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>310003; 389298</t>
+          <t>310617; 389773</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>497300; 565080</t>
+          <t>497854; 561438</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>526603; 600686</t>
+          <t>525831; 601377</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>496688; 568980</t>
+          <t>496219; 571859</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>761394; 1164682</t>
+          <t>769556; 1182120</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>237277; 274295</t>
+          <t>237421; 276383</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>232247; 276063</t>
+          <t>232439; 275822</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>245864; 292461</t>
+          <t>247294; 293015</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>304733; 347126</t>
+          <t>306794; 347854</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>266829; 302710</t>
+          <t>264720; 302428</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>294446; 334479</t>
+          <t>296034; 335405</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>288959; 334322</t>
+          <t>289655; 334421</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>332046; 366323</t>
+          <t>331223; 364648</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>511728; 564882</t>
+          <t>514854; 566782</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>537831; 597510</t>
+          <t>538259; 598497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546885; 612163</t>
+          <t>548012; 614620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>648415; 705940</t>
+          <t>646974; 700569</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>210136; 238977</t>
+          <t>210359; 239148</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>219790; 251379</t>
+          <t>220009; 251388</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>212003; 245546</t>
+          <t>210940; 246079</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>214430; 244083</t>
+          <t>214867; 245406</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>287974; 310510</t>
+          <t>287072; 311285</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>271407; 301392</t>
+          <t>272312; 302640</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>272893; 307998</t>
+          <t>273465; 307197</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>455492; 566574</t>
+          <t>458055; 568026</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>506641; 545005</t>
+          <t>504214; 544802</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>496940; 542230</t>
+          <t>497604; 543145</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>494526; 542136</t>
+          <t>493320; 543729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>673993; 845734</t>
+          <t>672680; 851809</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>180769; 197639</t>
+          <t>180988; 197923</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>207648; 229127</t>
+          <t>204872; 228312</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>199078; 220548</t>
+          <t>198488; 220966</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>214828; 236328</t>
+          <t>216586; 235363</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>310899; 326742</t>
+          <t>311806; 326613</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>355666; 374826</t>
+          <t>356498; 375849</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>350242; 375198</t>
+          <t>349335; 375838</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>374806; 390872</t>
+          <t>374792; 390626</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>497192; 521328</t>
+          <t>496791; 520188</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>569236; 598599</t>
+          <t>569458; 599113</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>556053; 590549</t>
+          <t>558152; 592086</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>595903; 622376</t>
+          <t>595871; 621752</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1342788; 1458215</t>
+          <t>1334686; 1458948</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1445255; 1572564</t>
+          <t>1454404; 1573064</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1270293; 1381491</t>
+          <t>1265887; 1383208</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1557120; 2116180</t>
+          <t>1563703; 2095632</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1870650; 1988583</t>
+          <t>1865497; 1982855</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1871924; 2000271</t>
+          <t>1874277; 1994639</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1629512; 1758713</t>
+          <t>1638475; 1758059</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1855580; 2301535</t>
+          <t>1855890; 2301980</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3234788; 3405160</t>
+          <t>3242413; 3406066</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3353430; 3524304</t>
+          <t>3351809; 3525395</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2930007; 3097352</t>
+          <t>2927561; 3102177</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3473685; 4140835</t>
+          <t>3474211; 4180808</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 26,2</t>
+          <t>18,42; 26,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,72; 28,97</t>
+          <t>20,24; 28,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,75; 22,63</t>
+          <t>14,61; 22,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,21; 26,82</t>
+          <t>14,21; 27,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,76; 32,48</t>
+          <t>24,33; 32,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,02; 32,66</t>
+          <t>24,15; 32,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,57; 25,65</t>
+          <t>17,46; 25,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 25,26</t>
+          <t>14,18; 25,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,97; 28,09</t>
+          <t>22,29; 28,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,42; 29,41</t>
+          <t>23,44; 29,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,95; 22,74</t>
+          <t>16,98; 22,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,47; 24,24</t>
+          <t>15,98; 24,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,69; 27,28</t>
+          <t>20,69; 27,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,39; 31,85</t>
+          <t>24,5; 31,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,51; 25,52</t>
+          <t>18,51; 25,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,84; 36,52</t>
+          <t>24,6; 35,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,37; 43,3</t>
+          <t>35,35; 43,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,12; 38,92</t>
+          <t>31,1; 38,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,98; 27,08</t>
+          <t>19,78; 26,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,36; 31,61</t>
+          <t>24,89; 33,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,52; 33,58</t>
+          <t>28,41; 33,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,59; 34,16</t>
+          <t>28,95; 34,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,2; 24,98</t>
+          <t>20,1; 25,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,68; 32,19</t>
+          <t>26,14; 33,18</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,32; 37,7</t>
+          <t>30,41; 38,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,24; 39,58</t>
+          <t>32,62; 39,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 27,49</t>
+          <t>20,6; 26,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,13; 38,51</t>
+          <t>29,26; 37,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,61; 52,32</t>
+          <t>44,6; 52,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,87; 48,35</t>
+          <t>40,58; 48,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,36; 37,9</t>
+          <t>30,72; 37,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,66; 40,23</t>
+          <t>33,76; 40,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,05; 44,39</t>
+          <t>38,79; 44,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,57; 43,24</t>
+          <t>37,48; 43,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,36; 31,55</t>
+          <t>26,72; 32,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,72; 38,24</t>
+          <t>32,34; 37,67</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,42; 47,91</t>
+          <t>38,13; 46,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,44; 45,59</t>
+          <t>37,11; 45,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,53; 42,35</t>
+          <t>34,35; 42,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,4; 83,65</t>
+          <t>43,07; 50,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,11; 64,51</t>
+          <t>55,86; 64,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,86; 54,12</t>
+          <t>46,17; 54,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,5; 48,03</t>
+          <t>39,64; 47,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,79; 54,95</t>
+          <t>49,53; 55,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,11; 54,26</t>
+          <t>48,21; 54,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42,72; 48,86</t>
+          <t>42,74; 48,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38,31; 44,15</t>
+          <t>38,49; 43,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,25; 74,11</t>
+          <t>47,1; 52,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,4; 71,47</t>
+          <t>61,19; 70,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,13; 64,23</t>
+          <t>54,12; 63,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,74; 61,31</t>
+          <t>51,24; 61,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55,28; 62,68</t>
+          <t>53,12; 61,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,53; 74,86</t>
+          <t>65,68; 74,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,11; 74,9</t>
+          <t>66,35; 75,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,3; 67,31</t>
+          <t>58,02; 67,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,71; 66,83</t>
+          <t>60,91; 66,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65,11; 71,68</t>
+          <t>64,97; 71,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,36; 68,23</t>
+          <t>61,81; 68,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56,22; 63,05</t>
+          <t>56,36; 62,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,79; 63,66</t>
+          <t>57,95; 62,98</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,9; 81,74</t>
+          <t>71,89; 81,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71,02; 81,15</t>
+          <t>70,79; 80,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,09; 73,6</t>
+          <t>63,22; 73,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59,07; 67,46</t>
+          <t>58,29; 66,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,71; 90,77</t>
+          <t>84,23; 90,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,93; 85,49</t>
+          <t>76,59; 85,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,39; 81,32</t>
+          <t>72,39; 81,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75,51; 93,63</t>
+          <t>73,13; 78,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79,34; 85,73</t>
+          <t>79,52; 85,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74,96; 81,83</t>
+          <t>75,21; 82,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69,28; 76,36</t>
+          <t>69,62; 76,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69,32; 87,78</t>
+          <t>67,04; 72,18</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,23; 94,3</t>
+          <t>85,39; 94,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,0; 91,38</t>
+          <t>82,92; 91,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,23; 85,98</t>
+          <t>77,77; 86,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77,24; 83,93</t>
+          <t>76,34; 83,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,38; 97,82</t>
+          <t>93,41; 97,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,65; 96,62</t>
+          <t>91,66; 96,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,3; 93,92</t>
+          <t>87,44; 93,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,73; 93,52</t>
+          <t>89,45; 93,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,36; 95,66</t>
+          <t>91,62; 95,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89,14; 93,78</t>
+          <t>89,03; 93,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84,93; 90,1</t>
+          <t>84,76; 89,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,35; 89,06</t>
+          <t>84,95; 88,86</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,73; 44,53</t>
+          <t>40,72; 44,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,44; 45,91</t>
+          <t>42,17; 45,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,29; 40,75</t>
+          <t>37,42; 40,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45,41; 60,85</t>
+          <t>43,74; 47,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,21; 58,68</t>
+          <t>55,26; 58,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,67; 56,06</t>
+          <t>52,73; 55,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,23; 49,6</t>
+          <t>46,06; 49,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,94; 63,18</t>
+          <t>51,61; 54,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,72; 51,17</t>
+          <t>48,72; 51,26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,99; 50,47</t>
+          <t>48,15; 50,48</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42,19; 44,71</t>
+          <t>42,2; 44,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,02; 58,99</t>
+          <t>48,13; 50,47</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76970</t>
+          <t>82445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56959</t>
+          <t>70907</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>133929</t>
+          <t>153352</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91246; 129428</t>
+          <t>90983; 129783</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94077; 131573</t>
+          <t>91935; 129238</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61876; 94909</t>
+          <t>61277; 93775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52854; 107285</t>
+          <t>57957; 110649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>115759; 151828</t>
+          <t>113741; 150316</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>103348; 140516</t>
+          <t>103882; 140733</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69523; 101529</t>
+          <t>69089; 100540</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38814; 78722</t>
+          <t>51186; 93330</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>211240; 270100</t>
+          <t>214306; 271727</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>207106; 260054</t>
+          <t>207263; 257606</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138144; 185355</t>
+          <t>138434; 186808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>102970; 172524</t>
+          <t>122875; 189032</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128996</t>
+          <t>143263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>131816</t>
+          <t>145382</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>260812</t>
+          <t>288645</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>152162; 200650</t>
+          <t>152199; 199549</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>167551; 218839</t>
+          <t>168308; 216574</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109295; 150724</t>
+          <t>109301; 150401</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105211; 154688</t>
+          <t>117316; 171551</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>221239; 270853</t>
+          <t>221084; 272529</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>189886; 237531</t>
+          <t>189795; 236382</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>112602; 152634</t>
+          <t>111478; 150780</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78466; 161511</t>
+          <t>124593; 168557</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>388090; 456999</t>
+          <t>386711; 456927</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>370970; 443208</t>
+          <t>375604; 443049</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>233131; 288277</t>
+          <t>232004; 290724</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>202569; 300776</t>
+          <t>255506; 324285</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181722</t>
+          <t>204853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>199190</t>
+          <t>228902</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>380913</t>
+          <t>433754</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>193646; 240804</t>
+          <t>194201; 243081</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>219820; 269913</t>
+          <t>222395; 271169</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138575; 183952</t>
+          <t>137802; 180280</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161319; 206187</t>
+          <t>181363; 230131</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>307675; 360907</t>
+          <t>307656; 360412</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>290517; 343678</t>
+          <t>288485; 343075</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>200820; 250643</t>
+          <t>203204; 250168</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>182360; 217927</t>
+          <t>209765; 250230</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>518760; 589699</t>
+          <t>515333; 586968</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>523238; 602145</t>
+          <t>522043; 599996</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>350704; 419798</t>
+          <t>355516; 428876</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>352429; 411884</t>
+          <t>401455; 467553</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>545481</t>
+          <t>326974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>362355</t>
+          <t>383976</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>907837</t>
+          <t>710950</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>199473; 248726</t>
+          <t>197942; 242984</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>230124; 280198</t>
+          <t>228057; 279399</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>223100; 273604</t>
+          <t>221938; 274694</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>402082; 740869</t>
+          <t>300902; 354157</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>289338; 332661</t>
+          <t>288014; 331631</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>282596; 333501</t>
+          <t>284523; 338178</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>256359; 311761</t>
+          <t>257327; 307640</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>310617; 389773</t>
+          <t>363133; 403537</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>497854; 561438</t>
+          <t>498861; 564547</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>525831; 601377</t>
+          <t>526007; 602877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>496219; 571859</t>
+          <t>498464; 568049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>769556; 1182120</t>
+          <t>674435; 745698</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>326301</t>
+          <t>344008</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>348357</t>
+          <t>387508</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>674658</t>
+          <t>731516</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>237421; 276383</t>
+          <t>236645; 273514</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>232439; 275822</t>
+          <t>232410; 272982</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>247294; 293015</t>
+          <t>244890; 291530</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>306794; 347854</t>
+          <t>319929; 369094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>264720; 302428</t>
+          <t>265334; 300703</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>296034; 335405</t>
+          <t>297135; 337004</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>289655; 334421</t>
+          <t>288267; 334053</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>331223; 364648</t>
+          <t>369424; 404190</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>514854; 566782</t>
+          <t>513704; 565116</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>538259; 598497</t>
+          <t>542198; 602037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>548012; 614620</t>
+          <t>549372; 612684</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>646974; 700569</t>
+          <t>700463; 761326</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229411</t>
+          <t>250622</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>511562</t>
+          <t>332668</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>740974</t>
+          <t>583291</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>210359; 239148</t>
+          <t>210337; 239085</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>220009; 251388</t>
+          <t>219302; 249746</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>210940; 246079</t>
+          <t>211373; 245027</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>214867; 245406</t>
+          <t>234367; 266038</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>287072; 311285</t>
+          <t>288851; 311763</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>272312; 302640</t>
+          <t>271129; 301050</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>273465; 307197</t>
+          <t>273452; 308052</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>458055; 568026</t>
+          <t>319754; 344267</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>504214; 544802</t>
+          <t>505358; 543164</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>497604; 543145</t>
+          <t>499261; 544512</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>493320; 543729</t>
+          <t>495776; 544901</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>672680; 851809</t>
+          <t>562726; 605835</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226029</t>
+          <t>246392</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>383552</t>
+          <t>417633</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>609581</t>
+          <t>664025</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>180988; 197923</t>
+          <t>179221; 197933</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>204872; 228312</t>
+          <t>207171; 228810</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>198488; 220966</t>
+          <t>199865; 221934</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>216586; 235363</t>
+          <t>234823; 258034</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>311806; 326613</t>
+          <t>311919; 326993</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>356498; 375849</t>
+          <t>356542; 375958</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>349335; 375838</t>
+          <t>349907; 375707</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>374792; 390626</t>
+          <t>407712; 425570</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>496791; 520188</t>
+          <t>498235; 520733</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>569458; 599113</t>
+          <t>568767; 598872</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>558152; 592086</t>
+          <t>557014; 591236</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>595871; 621752</t>
+          <t>648505; 678371</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1714911</t>
+          <t>1598557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1993792</t>
+          <t>1966976</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3708703</t>
+          <t>3565533</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1334686; 1458948</t>
+          <t>1334087; 1455877</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1454404; 1573064</t>
+          <t>1445018; 1567650</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1265887; 1383208</t>
+          <t>1270190; 1384774</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1563703; 2095632</t>
+          <t>1537537; 1660921</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1865497; 1982855</t>
+          <t>1867507; 1984856</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1874277; 1994639</t>
+          <t>1876130; 1990743</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1638475; 1758059</t>
+          <t>1632684; 1752258</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1855890; 2301980</t>
+          <t>1917711; 2026014</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3242413; 3406066</t>
+          <t>3242541; 3411872</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3351809; 3525395</t>
+          <t>3363111; 3526124</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2927561; 3102177</t>
+          <t>2928023; 3099135</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3474211; 4180808</t>
+          <t>3480317; 3649031</t>
         </is>
       </c>
     </row>
